--- a/03_Data_Operations/FMCG_Demand_Planning/FMCG_Demand_Planner_Example_v1.xlsx
+++ b/03_Data_Operations/FMCG_Demand_Planning/FMCG_Demand_Planner_Example_v1.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c04201e4fb2a04af/Desktop/Local Work Portfolio/GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c04201e4fb2a04af/Desktop/Local Work Portfolio/GitHub/Run_Work/03_Data_Operations/FMCG_Demand_Planning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="609" documentId="14_{7C3CE971-0282-4E1F-8BC4-A1B625E62A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{143090B7-231F-4726-B417-725B735B92EE}"/>
+  <xr:revisionPtr revIDLastSave="864" documentId="14_{7C3CE971-0282-4E1F-8BC4-A1B625E62A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E2DB5F1-84CB-4FE8-BAA4-41FB9727C35C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{698A86FF-035B-41C1-AB67-35A7EBBEA5FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{698A86FF-035B-41C1-AB67-35A7EBBEA5FF}"/>
   </bookViews>
   <sheets>
-    <sheet name="FMCG_Raw_Sales" sheetId="2" r:id="rId1"/>
-    <sheet name="Recount_List" sheetId="4" r:id="rId2"/>
-    <sheet name="DashBoard" sheetId="3" r:id="rId3"/>
-    <sheet name="Size_Map" sheetId="1" r:id="rId4"/>
+    <sheet name="DashBoard" sheetId="5" r:id="rId1"/>
+    <sheet name="FMCG_Raw_Sales" sheetId="2" r:id="rId2"/>
+    <sheet name="Recount_List" sheetId="4" r:id="rId3"/>
+    <sheet name="DashBoard_Data" sheetId="3" r:id="rId4"/>
+    <sheet name="Size_Map" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Recount_List!$K$1:$K$200</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Recount_List!$K$1:$O$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Recount_List!$K$1:$K$200</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Recount_List!$K$1:$O$200</definedName>
     <definedName name="rng_Recount">Recount_List!$K$1:$O$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -99,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="147">
   <si>
     <t>Product_Code</t>
   </si>
@@ -535,6 +536,12 @@
   <si>
     <t>Improvement = Before vs After</t>
   </si>
+  <si>
+    <t>Acceptable data increased significantly, while problem stock reduced.</t>
+  </si>
+  <si>
+    <t>Highest risk of Out-of_Stock issues</t>
+  </si>
 </sst>
 </file>
 
@@ -543,7 +550,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -652,6 +659,28 @@
       <name val="HP Simplified"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF9900"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF9900"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF9900"/>
+      <name val="HP Simplified"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -691,7 +720,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -909,12 +938,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -984,6 +1028,24 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1266,6 +1328,247 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="HP Simplified"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </left>
+        <right/>
+        <top style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </bottom>
+        <vertical style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </vertical>
+        <horizontal style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="HP Simplified"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </left>
+        <right style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </right>
+        <top style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </bottom>
+        <vertical style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </vertical>
+        <horizontal style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="HP Simplified"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </left>
+        <right style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </right>
+        <top style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </bottom>
+        <vertical style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </vertical>
+        <horizontal style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="HP Simplified"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </right>
+        <top style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </bottom>
+        <vertical style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </vertical>
+        <horizontal style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </left>
+        <right style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </right>
+        <top style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </top>
+        <bottom style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="HP Simplified"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="HP Simplified"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </left>
+        <right style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </vertical>
+        <horizontal style="hair">
+          <color theme="4" tint="-0.499984740745262"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2127,251 +2430,11 @@
       </fill>
       <alignment horizontal="general" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="HP Simplified"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </left>
-        <right/>
-        <top style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </bottom>
-        <vertical style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </vertical>
-        <horizontal style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="HP Simplified"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </left>
-        <right style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </right>
-        <top style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </bottom>
-        <vertical style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </vertical>
-        <horizontal style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="HP Simplified"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </left>
-        <right style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </right>
-        <top style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </bottom>
-        <vertical style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </vertical>
-        <horizontal style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="HP Simplified"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </right>
-        <top style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </bottom>
-        <vertical style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </vertical>
-        <horizontal style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </left>
-        <right style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </right>
-        <top style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </top>
-        <bottom style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="HP Simplified"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="HP Simplified"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="-0.249977111117893"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </left>
-        <right style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </vertical>
-        <horizontal style="hair">
-          <color theme="4" tint="-0.499984740745262"/>
-        </horizontal>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9900"/>
       <color rgb="FFFFFF99"/>
     </mruColors>
   </colors>
@@ -2407,30 +2470,35 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="FF9900"/>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="HP Simplified Hans" panose="020B0500000000000000" pitchFamily="34" charset="-122"/>
+                <a:ea typeface="HP Simplified Hans" panose="020B0500000000000000" pitchFamily="34" charset="-122"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" b="1"/>
-              <a:t>Percentage  SKU</a:t>
+              <a:rPr lang="en-ZA" sz="2400" b="0" i="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF9900"/>
+                </a:solidFill>
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Data Reliability Improved After Recount Process</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
-              <a:t>s  Validated</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" b="1"/>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.5107474310809186E-2"/>
+          <c:y val="6.3016132129824979E-4"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2444,15 +2512,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:srgbClr val="FF9900"/>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
+              <a:latin typeface="HP Simplified Hans" panose="020B0500000000000000" pitchFamily="34" charset="-122"/>
+              <a:ea typeface="HP Simplified Hans" panose="020B0500000000000000" pitchFamily="34" charset="-122"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
@@ -2464,7 +2529,7 @@
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -2472,24 +2537,32 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>DashBoard!$C$8</c:f>
+              <c:f>DashBoard_Data!$C$92</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Percentage</c:v>
+                  <c:v>Before</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
+            <a:pattFill prst="wdUpDiag">
+              <a:fgClr>
+                <a:schemeClr val="tx2">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:fgClr>
+              <a:bgClr>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:bgClr>
+            </a:pattFill>
+            <a:ln cap="sq">
               <a:solidFill>
-                <a:schemeClr val="accent3">
+                <a:schemeClr val="accent1">
                   <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
@@ -2502,19 +2575,31 @@
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="00B050"/>
-              </a:solidFill>
-              <a:ln>
+              <a:pattFill prst="wdUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln cap="sq">
                 <a:solidFill>
-                  <a:srgbClr val="00B050"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-DDDC-45D2-B7CD-D004363C0C91}"/>
+                <c16:uniqueId val="{00000001-2813-4D15-A450-1A5641FE672C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2523,19 +2608,31 @@
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFC000"/>
-              </a:solidFill>
-              <a:ln>
+              <a:pattFill prst="wdUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln cap="sq">
                 <a:solidFill>
-                  <a:srgbClr val="FFC000"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-DDDC-45D2-B7CD-D004363C0C91}"/>
+                <c16:uniqueId val="{00000003-2813-4D15-A450-1A5641FE672C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2544,25 +2641,37 @@
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln>
+              <a:pattFill prst="wdUpDiag">
+                <a:fgClr>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln cap="sq">
                 <a:solidFill>
-                  <a:srgbClr val="C00000"/>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="75000"/>
+                  </a:schemeClr>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-DDDC-45D2-B7CD-D004363C0C91}"/>
+                <c16:uniqueId val="{00000005-2813-4D15-A450-1A5641FE672C}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>DashBoard!$B$9:$B$11</c:f>
+              <c:f>DashBoard_Data!$B$93:$B$95</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -2579,7 +2688,116 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DashBoard!$C$9:$C$11</c:f>
+              <c:f>DashBoard_Data!$C$93:$C$95</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.27272727272727271</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.42045454545454547</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.30681818181818182</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2813-4D15-A450-1A5641FE672C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>DashBoard_Data!$D$92</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>After</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF9900"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF9900"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF9900"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF9900"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-2813-4D15-A450-1A5641FE672C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF9900"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF9900"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-2813-4D15-A450-1A5641FE672C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>DashBoard_Data!$B$93:$B$95</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Acceptable</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Check</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Problem</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>DashBoard_Data!$D$93:$D$95</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2597,7 +2815,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DDDC-45D2-B7CD-D004363C0C91}"/>
+              <c16:uniqueId val="{0000000B-2813-4D15-A450-1A5641FE672C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2609,18 +2827,17 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="24"/>
-        <c:overlap val="-27"/>
-        <c:axId val="1958718591"/>
-        <c:axId val="1958702271"/>
+        <c:gapWidth val="23"/>
+        <c:axId val="1958678751"/>
+        <c:axId val="1958670111"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1958718591"/>
+        <c:axId val="1958678751"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -2643,12 +2860,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="FF9900"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2658,7 +2872,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1958702271"/>
+        <c:crossAx val="1958670111"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2666,12 +2880,12 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1958702271"/>
+        <c:axId val="1958670111"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -2704,10 +2918,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="FF9900"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -2717,9 +2928,10 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1958718591"/>
+        <c:crossAx val="1958678751"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="0.1"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2742,16 +2954,12 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1">
-        <a:lumMod val="95000"/>
+      <a:schemeClr val="accent1">
+        <a:lumMod val="50000"/>
       </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="accent1">
-          <a:lumMod val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -2769,668 +2977,12 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" b="1"/>
-              <a:t>Improvement in Reliable</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" b="1" baseline="0"/>
-              <a:t> Data Before and After</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" b="1"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>DashBoard!$C$92</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Before</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="75000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-956A-4135-BF7F-5A4C5751EBD2}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFC000"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="FFC000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-956A-4135-BF7F-5A4C5751EBD2}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000006-956A-4135-BF7F-5A4C5751EBD2}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>DashBoard!$B$93:$B$95</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Acceptable</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Check</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Problem</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>DashBoard!$C$93:$C$95</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.27272727272727271</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.42045454545454547</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.30681818181818182</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-956A-4135-BF7F-5A4C5751EBD2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>DashBoard!$D$92</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>After</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                  <a:lumOff val="40000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent3">
-                    <a:lumMod val="60000"/>
-                    <a:lumOff val="40000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-956A-4135-BF7F-5A4C5751EBD2}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FFFF99"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="FFFF00"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-956A-4135-BF7F-5A4C5751EBD2}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>DashBoard!$B$93:$B$95</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Acceptable</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Check</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Problem</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>DashBoard!$D$93:$D$95</c:f>
-              <c:numCache>
-                <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>0.63636363636363635</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.11363636363636363</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-956A-4135-BF7F-5A4C5751EBD2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="39"/>
-        <c:overlap val="-27"/>
-        <c:axId val="1958678751"/>
-        <c:axId val="1958670111"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1958678751"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1958670111"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1958670111"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1958678751"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1">
-        <a:lumMod val="95000"/>
-      </a:schemeClr>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="accent1">
-          <a:lumMod val="50000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
+    <c:pageSetup orientation="portrait"/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3973,581 +3525,260 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>82550</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>387350</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="3" name="Group 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01C0539C-AC53-E0F5-64A0-AADB10BC10F7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D21BC6-AADC-41B5-DC96-5791A47431EB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>577850</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19BF3FD1-1239-63D5-769B-ABA3D6FA80D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="66675" y="3968750"/>
+          <a:ext cx="5848350" cy="4168775"/>
+          <a:chOff x="66675" y="4114800"/>
+          <a:chExt cx="5695950" cy="4314825"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="2" name="Chart 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44B7F6B3-1A1C-4EA0-BC5E-B4DF1372BC59}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGraphicFramePr>
+            <a:graphicFrameLocks/>
+          </xdr:cNvGraphicFramePr>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="66675" y="4114800"/>
+          <a:ext cx="5638800" cy="4314825"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="TextBox 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1889BFB1-11E9-15BC-D5EC-2A6DCF9C51CC}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3822700" y="4886325"/>
+            <a:ext cx="1939925" cy="209550"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln w="9525" cmpd="sng">
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="dk1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="en-ZA" sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF9900"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>BEFORE </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-ZA" sz="1100" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="FF9900"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>                </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-ZA" sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="FF9900"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>AFTER</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="Rectangle 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19E0F0F5-300C-7F9C-C50B-8A76367B2123}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4454526" y="4946649"/>
+            <a:ext cx="269875" cy="149225"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:pattFill prst="wdUpDiag">
+            <a:fgClr>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
+              </a:schemeClr>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx2">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-ZA" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="Rectangle 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{071485F4-0C2F-467A-8A03-55DAE0A03DD3}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5267326" y="4946649"/>
+            <a:ext cx="295275" cy="155575"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="FF9900"/>
+          </a:solidFill>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="en-ZA" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4560,79 +3791,79 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3BFD5D0D-CFBC-42AA-81C3-119686D814B4}" name="tbl_Fact_Sales" displayName="tbl_Fact_Sales" ref="A1:AG89" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" tableBorderDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3BFD5D0D-CFBC-42AA-81C3-119686D814B4}" name="tbl_Fact_Sales" displayName="tbl_Fact_Sales" ref="A1:AG89" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59" tableBorderDxfId="58">
   <autoFilter ref="A1:AG89" xr:uid="{3BFD5D0D-CFBC-42AA-81C3-119686D814B4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q89">
     <sortCondition ref="C2:C89"/>
   </sortState>
   <tableColumns count="33">
-    <tableColumn id="1" xr3:uid="{FBF50E5E-E998-40B0-A6E8-DE9E12BACD03}" name="Product_Code" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{5C4D9D9B-C66E-4C8F-9DD1-C7338E9EED63}" name="EAN" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{B25FE605-5776-4E03-81F9-61BE16BBF767}" name="Product_Description" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{2BDDD029-92D5-4152-84CA-8098DFD34F34}" name="Size" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{82EE0334-6851-45E1-B4CF-FD2ACCCB473C}" name="SOH" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{3A5FD4E6-01B9-444C-8032-EBD506A37AD3}" name="Sales_at_CP" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{A4D33ADF-CBC1-4AFB-B764-3F5D4F82A2A8}" name="Sales_Quantity" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{A8A0E6E9-111D-4850-9AA2-21894B00A5DF}" name="GP %" dataDxfId="41" dataCellStyle="Per cent"/>
-    <tableColumn id="9" xr3:uid="{74807D57-84D7-4240-997F-93CDCCC580AD}" name="Units_Sold" dataDxfId="40"/>
-    <tableColumn id="10" xr3:uid="{8C8E5D76-D029-4C7A-AA3B-134343D3D0DE}" name="Cases_Sold" dataDxfId="39"/>
-    <tableColumn id="11" xr3:uid="{5434C376-D091-4965-A2C9-CFD1ED770400}" name="Size_Clean" dataDxfId="38"/>
-    <tableColumn id="12" xr3:uid="{061356C9-2321-4583-AEC7-568F23CD193A}" name="GP_Percentage" dataDxfId="37" dataCellStyle="Per cent"/>
-    <tableColumn id="13" xr3:uid="{54C92765-7D8E-4759-960A-C16E4C0C8C42}" name="Pack_Size" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{FBF50E5E-E998-40B0-A6E8-DE9E12BACD03}" name="Product_Code" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{5C4D9D9B-C66E-4C8F-9DD1-C7338E9EED63}" name="EAN" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{B25FE605-5776-4E03-81F9-61BE16BBF767}" name="Product_Description" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{2BDDD029-92D5-4152-84CA-8098DFD34F34}" name="Size" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{82EE0334-6851-45E1-B4CF-FD2ACCCB473C}" name="SOH" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{3A5FD4E6-01B9-444C-8032-EBD506A37AD3}" name="Sales_at_CP" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{A4D33ADF-CBC1-4AFB-B764-3F5D4F82A2A8}" name="Sales_Quantity" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{A8A0E6E9-111D-4850-9AA2-21894B00A5DF}" name="GP %" dataDxfId="50" dataCellStyle="Per cent"/>
+    <tableColumn id="9" xr3:uid="{74807D57-84D7-4240-997F-93CDCCC580AD}" name="Units_Sold" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{8C8E5D76-D029-4C7A-AA3B-134343D3D0DE}" name="Cases_Sold" dataDxfId="48"/>
+    <tableColumn id="11" xr3:uid="{5434C376-D091-4965-A2C9-CFD1ED770400}" name="Size_Clean" dataDxfId="47"/>
+    <tableColumn id="12" xr3:uid="{061356C9-2321-4583-AEC7-568F23CD193A}" name="GP_Percentage" dataDxfId="46" dataCellStyle="Per cent"/>
+    <tableColumn id="13" xr3:uid="{54C92765-7D8E-4759-960A-C16E4C0C8C42}" name="Pack_Size" dataDxfId="45">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[Size_Clean]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{F5C7BF95-673A-49F7-BB00-DB779D4D95D4}" name="Units_Per_Pack" dataDxfId="35">
+    <tableColumn id="14" xr3:uid="{F5C7BF95-673A-49F7-BB00-DB779D4D95D4}" name="Units_Per_Pack" dataDxfId="44">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_Fact_Sales[[#This Row],[Pack_Size]], tbl_Size_Map[Size_Clean], tbl_Size_Map[Units_Per_Case])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{5DCE994E-1ACA-4E6C-AC4D-00D76CFA9D0B}" name="Cases_Sold2" dataDxfId="34">
+    <tableColumn id="16" xr3:uid="{5DCE994E-1ACA-4E6C-AC4D-00D76CFA9D0B}" name="Cases_Sold2" dataDxfId="43">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[Units_Sold]] / tbl_Fact_Sales[[#This Row],[Units_Per_Pack]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{8F0D69E7-4991-4AB3-9343-C0833060C836}" name="Cases_SOH" dataDxfId="33">
+    <tableColumn id="17" xr3:uid="{8F0D69E7-4991-4AB3-9343-C0833060C836}" name="Cases_SOH" dataDxfId="42">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[SOH]] / tbl_Fact_Sales[[#This Row],[Units_Per_Pack]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{329987C9-9D6E-4934-A822-DBB3C1D51059}" name="Parent_Product" dataDxfId="32"/>
-    <tableColumn id="19" xr3:uid="{FE4D6C28-1702-41DB-B4AB-7526EFF01DC0}" name="Parent_Total_Units" dataDxfId="31">
+    <tableColumn id="18" xr3:uid="{329987C9-9D6E-4934-A822-DBB3C1D51059}" name="Parent_Product" dataDxfId="41"/>
+    <tableColumn id="19" xr3:uid="{FE4D6C28-1702-41DB-B4AB-7526EFF01DC0}" name="Parent_Total_Units" dataDxfId="40">
       <calculatedColumnFormula>SUMIFS(tbl_Fact_Sales[Units_Sold], tbl_Fact_Sales[Parent_Product], tbl_Fact_Sales[[#This Row],[Parent_Product]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{AEAB2CE3-1DB0-495D-A40C-81B4F37155A9}" name="Balance_Status" dataDxfId="30">
+    <tableColumn id="20" xr3:uid="{AEAB2CE3-1DB0-495D-A40C-81B4F37155A9}" name="Balance_Status" dataDxfId="39">
       <calculatedColumnFormula>IF(ABS(tbl_Fact_Sales[[#This Row],[Parent_Total_Units]])&lt;0.0001, "Balanced", "Investigate")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{558FDB8A-7EB6-4EFE-BB1C-FD7A3A2D8A59}" name="Variance" dataDxfId="29">
+    <tableColumn id="21" xr3:uid="{558FDB8A-7EB6-4EFE-BB1C-FD7A3A2D8A59}" name="Variance" dataDxfId="38">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[Parent_Total_Units]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{539DD50A-D519-47C5-A795-21B7E0F0327F}" name="Divergence" dataDxfId="28">
+    <tableColumn id="22" xr3:uid="{539DD50A-D519-47C5-A795-21B7E0F0327F}" name="Divergence" dataDxfId="37">
       <calculatedColumnFormula>IF(ABS(tbl_Fact_Sales[[#This Row],[Parent_Total_Units]])&lt;=50, "Acceptable", IF(ABS(tbl_Fact_Sales[[#This Row],[Parent_Total_Units]])&lt;=250, "Check", "Problem"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{6F5038A5-20FE-48DA-9417-E8D906652F9F}" name="Daily_Demand" dataDxfId="27">
+    <tableColumn id="15" xr3:uid="{6F5038A5-20FE-48DA-9417-E8D906652F9F}" name="Daily_Demand" dataDxfId="36">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[Cases_Sold2]]/7</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{51BA2013-E687-4625-84B7-08DDB146428D}" name="Safety_Stock" dataDxfId="26">
+    <tableColumn id="23" xr3:uid="{51BA2013-E687-4625-84B7-08DDB146428D}" name="Safety_Stock" dataDxfId="35">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[Daily_Demand]]*2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{5EC22CE9-3B60-4526-BA7F-87F35A0E1DF2}" name="Notes1" dataDxfId="25"/>
-    <tableColumn id="31" xr3:uid="{A4021B2A-E6F2-471D-BDE1-63B561955C16}" name="Notes2" dataDxfId="24"/>
-    <tableColumn id="25" xr3:uid="{65468168-BACF-4F66-993E-1CE6B53CEBEE}" name="Required_Stock" dataDxfId="23">
+    <tableColumn id="24" xr3:uid="{5EC22CE9-3B60-4526-BA7F-87F35A0E1DF2}" name="Notes1" dataDxfId="34"/>
+    <tableColumn id="31" xr3:uid="{A4021B2A-E6F2-471D-BDE1-63B561955C16}" name="Notes2" dataDxfId="33"/>
+    <tableColumn id="25" xr3:uid="{65468168-BACF-4F66-993E-1CE6B53CEBEE}" name="Required_Stock" dataDxfId="32">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[Daily_Demand]]*10 + tbl_Fact_Sales[[#This Row],[Safety_Stock]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{4761DDAC-202C-4CC2-A6F1-C29DCA74C92C}" name="Suggested_Order" dataDxfId="22">
+    <tableColumn id="26" xr3:uid="{4761DDAC-202C-4CC2-A6F1-C29DCA74C92C}" name="Suggested_Order" dataDxfId="31">
       <calculatedColumnFormula>MAX(0, tbl_Fact_Sales[[#This Row],[Required_Stock]] - tbl_Fact_Sales[[#This Row],[Cases_SOH]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{FB6DEE57-F382-46E2-97CF-B3990F002A45}" name="Days_of_Cover" dataDxfId="21">
+    <tableColumn id="27" xr3:uid="{FB6DEE57-F382-46E2-97CF-B3990F002A45}" name="Days_of_Cover" dataDxfId="30">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[Cases_SOH]] / tbl_Fact_Sales[[#This Row],[Daily_Demand]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{507A10DD-947A-4994-849D-55E1299D91CC}" name="Planning_Priority" dataDxfId="20">
+    <tableColumn id="28" xr3:uid="{507A10DD-947A-4994-849D-55E1299D91CC}" name="Planning_Priority" dataDxfId="29">
       <calculatedColumnFormula>tbl_Fact_Sales[[#This Row],[Suggested_Order]] * tbl_Fact_Sales[[#This Row],[Daily_Demand]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{A8EBBDFB-89FD-402B-B4E5-5ACF0ADED2BF}" name="Helper1" dataDxfId="19">
+    <tableColumn id="30" xr3:uid="{A8EBBDFB-89FD-402B-B4E5-5ACF0ADED2BF}" name="Helper1" dataDxfId="28">
       <calculatedColumnFormula>TRIM(tbl_Fact_Sales[[#This Row],[Parent_Product]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{2C763877-A33E-435F-BC30-F5D4E662CE93}" name="Adjusted_SOH" dataDxfId="18">
+    <tableColumn id="33" xr3:uid="{2C763877-A33E-435F-BC30-F5D4E662CE93}" name="Adjusted_SOH" dataDxfId="27">
       <calculatedColumnFormula array="1">IF(_xlfn.XLOOKUP(tbl_Fact_Sales[[#This Row],[Product_Code]], INDEX(rng_Recount, 0, 3), INDEX(rng_Recount, 0, 4), "") ="", tbl_Fact_Sales[[#This Row],[Cases_SOH]], _xlfn.XLOOKUP(tbl_Fact_Sales[[#This Row],[Product_Code]], INDEX(rng_Recount, 0, 3), INDEX(rng_Recount, 0, 4)))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{A6BEEC7E-110E-41FB-AFAA-AEEA58464324}" name="Recount_Variance" dataDxfId="17">
+    <tableColumn id="36" xr3:uid="{A6BEEC7E-110E-41FB-AFAA-AEEA58464324}" name="Recount_Variance" dataDxfId="26">
       <calculatedColumnFormula>ABS(tbl_Fact_Sales[[#This Row],[Required_Stock]] - tbl_Fact_Sales[[#This Row],[Adjusted_SOH]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{CBECE598-7FE0-44FC-9D0F-E94F4039F958}" name="Recount_Divergence" dataDxfId="16">
+    <tableColumn id="39" xr3:uid="{CBECE598-7FE0-44FC-9D0F-E94F4039F958}" name="Recount_Divergence" dataDxfId="25">
       <calculatedColumnFormula>IF(tbl_Fact_Sales[[#This Row],[Recount_Variance]]&lt;=10, "Acceptable", IF(tbl_Fact_Sales[[#This Row],[Recount_Variance]]&lt;=50, "Check", "Problem"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4641,19 +3872,19 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{967F5D14-9A89-4257-A6BB-3166AA44CE8A}" name="Table1" displayName="Table1" ref="A37:D88" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{967F5D14-9A89-4257-A6BB-3166AA44CE8A}" name="Table1" displayName="Table1" ref="A37:D88" totalsRowShown="0" headerRowDxfId="24" dataDxfId="22" headerRowBorderDxfId="23" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A37:D88" xr:uid="{967F5D14-9A89-4257-A6BB-3166AA44CE8A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{2C725611-C0DC-49C2-B916-2BC1BBE7378B}" name="Product" dataDxfId="55">
+    <tableColumn id="1" xr3:uid="{2C725611-C0DC-49C2-B916-2BC1BBE7378B}" name="Product" dataDxfId="19">
       <calculatedColumnFormula>TRIM(_xlfn.XLOOKUP(tbl_Fact_Sales[[#This Row],[Product_Code]], tbl_Fact_Sales[Product_Code], tbl_Fact_Sales[Helper1]) &amp; " " &amp; _xlfn.XLOOKUP(tbl_Fact_Sales[[#This Row],[Product_Code]], tbl_Fact_Sales[Product_Code], tbl_Fact_Sales[Size_Clean]))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{90FB852E-B155-4949-A75B-5908307967E6}" name="Suggested Order" dataDxfId="54">
+    <tableColumn id="2" xr3:uid="{90FB852E-B155-4949-A75B-5908307967E6}" name="Suggested Order" dataDxfId="18">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_Fact_Sales[[#This Row],[Product_Code]], tbl_Fact_Sales[Product_Code], tbl_Fact_Sales[Suggested_Order])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F75C4C05-7B03-4052-94C0-2A98B2D3BD1F}" name="Days Cover" dataDxfId="53">
+    <tableColumn id="3" xr3:uid="{F75C4C05-7B03-4052-94C0-2A98B2D3BD1F}" name="Days Cover" dataDxfId="17">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_Fact_Sales[[#This Row],[Product_Code]], tbl_Fact_Sales[Product_Code], tbl_Fact_Sales[Days_of_Cover])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{D0A028C0-8F78-4E8E-8BB7-392C3D2B0736}" name="Status" dataDxfId="52">
+    <tableColumn id="4" xr3:uid="{D0A028C0-8F78-4E8E-8BB7-392C3D2B0736}" name="Status" dataDxfId="16">
       <calculatedColumnFormula>_xlfn.XLOOKUP(tbl_Fact_Sales[[#This Row],[Product_Code]], tbl_Fact_Sales[Product_Code], tbl_Fact_Sales[Recount_Divergence])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5004,23 +4235,610 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DCB8FA5-B778-4713-BA80-665BB59A8A99}">
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="6.54296875" customWidth="1"/>
+    <col min="5" max="5" width="3.7265625" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="7" width="11.26953125" customWidth="1"/>
+    <col min="8" max="8" width="7.54296875" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="51"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="51"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="51"/>
+    </row>
+    <row r="4" spans="1:10" s="56" customFormat="1" ht="28" x14ac:dyDescent="0.35">
+      <c r="A4" s="52"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="H4" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="J4" s="52"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="51"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="51"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="51"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="51"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="51"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="51"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="51"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+      <c r="J10" s="51"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="51"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+      <c r="J12" s="51"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+      <c r="J13" s="51"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="51"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="51"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="51"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" s="51"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18" s="51"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20" s="51"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="51"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21" s="51"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22" s="51"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23" s="51"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A24" s="51"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A25" s="51"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A26" s="51"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A27" s="51"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A28" s="51"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="51"/>
+      <c r="J28" s="51"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A29" s="51"/>
+      <c r="B29" s="51"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="51"/>
+      <c r="E29" s="51"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A30" s="51"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="51"/>
+      <c r="E30" s="51"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A31" s="51"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" s="51"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="51"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A34" s="51"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="51"/>
+      <c r="E34" s="51"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="51"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A35" s="51"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="51"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="51"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="51"/>
+      <c r="H35" s="51"/>
+      <c r="I35" s="51"/>
+      <c r="J35" s="51"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A36" s="51"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+      <c r="I36" s="51"/>
+      <c r="J36" s="51"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A37" s="51"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A38" s="51"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A39" s="51"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="51"/>
+      <c r="I39" s="51"/>
+      <c r="J39" s="51"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="51"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="51"/>
+      <c r="H40" s="51"/>
+      <c r="I40" s="51"/>
+      <c r="J40" s="51"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="51"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" s="51"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="51"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="51"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="51"/>
+      <c r="I43" s="51"/>
+      <c r="J43" s="51"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="51"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="51"/>
+      <c r="I44" s="51"/>
+      <c r="J44" s="51"/>
+    </row>
+    <row r="45" spans="1:10" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A45" s="58" t="s">
+        <v>145</v>
+      </c>
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="58"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="51"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="51"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="51"/>
+      <c r="J46" s="51"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A45:J45"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF419915-3B0E-4CD6-8B6B-1A945F0665A3}">
   <dimension ref="A1:AG91"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.1796875" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.7265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.54296875" style="4" customWidth="1"/>
     <col min="5" max="5" width="6.7265625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.54296875" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.26953125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.36328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.453125" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.7265625" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.1796875" style="4" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.54296875" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="16.54296875" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.54296875" style="7" bestFit="1" customWidth="1"/>
@@ -5035,12 +4853,12 @@
     <col min="25" max="25" width="9.26953125" style="4" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="16.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="18.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.81640625" style="4" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="18" style="4" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="24.1796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="23.90625" style="4" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.08984375" style="4" customWidth="1"/>
-    <col min="33" max="33" width="20.90625" style="4" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23.81640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.1796875" style="4" customWidth="1"/>
+    <col min="33" max="33" width="20.81640625" style="4" bestFit="1" customWidth="1"/>
     <col min="34" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
@@ -15325,7 +15143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FD64BE-3487-4274-B06C-542EA0DB46CF}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:O201"/>
@@ -15341,8 +15159,8 @@
     <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="23.90625" customWidth="1"/>
-    <col min="13" max="13" width="23.90625" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="23.81640625" customWidth="1"/>
+    <col min="13" max="13" width="23.81640625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="43" customWidth="1"/>
   </cols>
@@ -17908,18 +17726,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86EF1FE5-C3F3-4B3C-91A8-1574FC2C8DF3}">
   <dimension ref="A1:F122"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.90625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.81640625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.1796875" style="9" customWidth="1"/>
     <col min="3" max="3" width="14.54296875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.7265625" style="9" customWidth="1"/>
     <col min="6" max="8" width="8.7265625" style="9"/>
-    <col min="9" max="13" width="15.6328125" style="9" customWidth="1"/>
+    <col min="9" max="13" width="15.54296875" style="9" customWidth="1"/>
     <col min="14" max="16384" width="8.7265625" style="9"/>
   </cols>
   <sheetData>
@@ -19011,35 +18829,35 @@
       <c r="A116"/>
     </row>
     <row r="118" spans="1:6" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A118" s="51" t="s">
+      <c r="A118" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="B118" s="51"/>
-      <c r="C118" s="51"/>
-      <c r="D118" s="51"/>
-      <c r="E118" s="51"/>
-      <c r="F118" s="51"/>
+      <c r="B118" s="59"/>
+      <c r="C118" s="59"/>
+      <c r="D118" s="59"/>
+      <c r="E118" s="59"/>
+      <c r="F118" s="59"/>
     </row>
     <row r="120" spans="1:6" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A120" s="53" t="s">
+      <c r="A120" s="61" t="s">
         <v>144</v>
       </c>
-      <c r="B120" s="53"/>
-      <c r="C120" s="53"/>
-      <c r="D120" s="53"/>
-      <c r="E120" s="53"/>
-      <c r="F120" s="53"/>
+      <c r="B120" s="61"/>
+      <c r="C120" s="61"/>
+      <c r="D120" s="61"/>
+      <c r="E120" s="61"/>
+      <c r="F120" s="61"/>
     </row>
     <row r="122" spans="1:6" ht="22" x14ac:dyDescent="0.4">
-      <c r="A122" s="52">
+      <c r="A122" s="60">
         <f>D93-C93</f>
         <v>0.36363636363636365</v>
       </c>
-      <c r="B122" s="52"/>
-      <c r="C122" s="52"/>
-      <c r="D122" s="52"/>
-      <c r="E122" s="52"/>
-      <c r="F122" s="52"/>
+      <c r="B122" s="60"/>
+      <c r="C122" s="60"/>
+      <c r="D122" s="60"/>
+      <c r="E122" s="60"/>
+      <c r="F122" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -19064,14 +18882,13 @@
     <brk id="35" max="16383" man="1"/>
     <brk id="88" max="16383" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE4C36A-FF96-4D6C-87C3-1924C30AB2B4}">
   <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
